--- a/data/northstar/Northstar-Disposition-Analysis-v3.xlsx
+++ b/data/northstar/Northstar-Disposition-Analysis-v3.xlsx
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Produced 2026-08-14 by Aberdeen Advisors' Application Rationalization engine. Source: your revised 20-application sample dataset (F0BQ93YLL22.xlsx, 12 sheets), unchanged since v2. Your file was opened read-only and is unchanged. The v1 and v2 workbooks and their scripts are untouched and still on disk beside this one.</t>
+          <t>Produced 2026-08-14 by Aberdeen Advisors' Application Rationalization engine. Source: your revised 20-application sample dataset (healthcare_app_rationalization_sample_20-with-risk.xlsx, 12 sheets), unchanged since v2. Your file was opened read-only and is unchanged. The v1 and v2 workbooks and their scripts are untouched and still on disk beside this one.</t>
         </is>
       </c>
     </row>
